--- a/files/OnlineAppendixBunDeWinter2019.xlsx
+++ b/files/OnlineAppendixBunDeWinter2019.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11550" firstSheet="7" activeTab="11"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11550"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2127" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2126" uniqueCount="701">
   <si>
     <t>micro</t>
   </si>
@@ -2118,9 +2118,6 @@
   </si>
   <si>
     <t>Predicted permanent standard deviation, capital wedge (tau_K), period 2001-2017</t>
-  </si>
-  <si>
-    <t>Estimated coefficients Doris et al. (2013), labor wedge (tau_L), period 2001-2017</t>
   </si>
   <si>
     <t>Predicted permanent standard deviation, labor wedge (tau_L), period 2001-2017</t>
@@ -2152,7 +2149,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2201,6 +2198,21 @@
       <i/>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
       <name val="Verdana"/>
       <family val="2"/>
     </font>
@@ -2257,11 +2269,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
@@ -2410,8 +2423,15 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
@@ -2695,7 +2715,7 @@
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" style="16" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24" style="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="109.140625" style="16" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.140625" style="7"/>
     <col min="5" max="16384" width="9.140625" style="16"/>
@@ -2711,7 +2731,7 @@
       <c r="D2" s="21"/>
     </row>
     <row r="3" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="62" t="s">
         <v>618</v>
       </c>
       <c r="C3" s="26" t="s">
@@ -2720,7 +2740,7 @@
       <c r="D3" s="28"/>
     </row>
     <row r="4" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="62" t="s">
         <v>619</v>
       </c>
       <c r="C4" s="26" t="s">
@@ -2729,7 +2749,7 @@
       <c r="D4" s="28"/>
     </row>
     <row r="5" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="62" t="s">
         <v>620</v>
       </c>
       <c r="C5" s="26" t="s">
@@ -2738,7 +2758,7 @@
       <c r="D5" s="28"/>
     </row>
     <row r="6" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="62" t="s">
         <v>621</v>
       </c>
       <c r="C6" s="26" t="s">
@@ -2747,7 +2767,7 @@
       <c r="D6" s="28"/>
     </row>
     <row r="7" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="62" t="s">
         <v>622</v>
       </c>
       <c r="C7" s="26" t="s">
@@ -2756,7 +2776,7 @@
       <c r="D7" s="28"/>
     </row>
     <row r="8" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="62" t="s">
         <v>623</v>
       </c>
       <c r="C8" s="26" t="s">
@@ -2765,7 +2785,7 @@
       <c r="D8" s="28"/>
     </row>
     <row r="9" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="62" t="s">
         <v>624</v>
       </c>
       <c r="C9" s="26" t="s">
@@ -2774,7 +2794,7 @@
       <c r="D9" s="28"/>
     </row>
     <row r="10" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="62" t="s">
         <v>625</v>
       </c>
       <c r="C10" s="26" t="s">
@@ -2783,43 +2803,58 @@
       <c r="D10" s="28"/>
     </row>
     <row r="11" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="62" t="s">
         <v>626</v>
       </c>
       <c r="C11" s="26" t="s">
+        <v>697</v>
+      </c>
+      <c r="D11" s="28"/>
+    </row>
+    <row r="12" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="62" t="s">
+        <v>627</v>
+      </c>
+      <c r="C12" s="26" t="s">
         <v>698</v>
       </c>
-      <c r="D11" s="28"/>
-    </row>
-    <row r="12" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="26" t="s">
-        <v>627</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>699</v>
-      </c>
       <c r="D12" s="28"/>
     </row>
     <row r="13" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="62" t="s">
         <v>628</v>
       </c>
       <c r="C13" s="26" t="s">
+        <v>695</v>
+      </c>
+      <c r="D13" s="28"/>
+    </row>
+    <row r="14" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="63" t="s">
+        <v>629</v>
+      </c>
+      <c r="C14" s="44" t="s">
         <v>696</v>
       </c>
-      <c r="D13" s="28"/>
-    </row>
-    <row r="14" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="44" t="s">
-        <v>629</v>
-      </c>
-      <c r="C14" s="44" t="s">
-        <v>697</v>
-      </c>
       <c r="D14" s="28"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B3" location="tau_k_prob!A1" display="tau_k_prob"/>
+    <hyperlink ref="B4" location="tau_k_prob_margins!A1" display="tau_k_prob_margins"/>
+    <hyperlink ref="B5" location="tau_k_prob_interact!A1" display="tau_k_prob_interact"/>
+    <hyperlink ref="B6" location="tau_k_prob_ev!A1" display="tau_k_prob_ev"/>
+    <hyperlink ref="B7" location="tau_l_prob!A1" display="tau_l_prob"/>
+    <hyperlink ref="B8" location="tau_l_prob_margins!A1" display="tau_l_prob_margins"/>
+    <hyperlink ref="B9" location="tau_l_prob_interact!A1" display="tau_l_prob_interact"/>
+    <hyperlink ref="B10" location="tau_l_prob_ev!A1" display="tau_l_prob_ev"/>
+    <hyperlink ref="B11" location="ln_mrpk_edmodel!A1" display="ln_mrpk_edmodel"/>
+    <hyperlink ref="B12" location="ln_mrpl_edmodel!A1" display="ln_mrpl_edmodel"/>
+    <hyperlink ref="B13" location="ln_tau_k_edmodel!A1" display="ln_tau_k_edmodel"/>
+    <hyperlink ref="B14" location="ln_tau_l_edmodel!A1" display="ln_tau_l_edmodel"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -12064,7 +12099,7 @@
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B64" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="65" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -13101,9 +13136,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B1" s="1" t="s">
-        <v>694</v>
-      </c>
+      <c r="B1" s="1"/>
     </row>
     <row r="2" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="60" t="s">
@@ -14681,7 +14714,7 @@
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="43" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -15482,7 +15515,7 @@
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B64" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="65" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/files/OnlineAppendixBunDeWinter2019.xlsx
+++ b/files/OnlineAppendixBunDeWinter2019.xlsx
@@ -2399,6 +2399,12 @@
     <xf numFmtId="3" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -2409,6 +2415,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2416,18 +2428,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2731,7 +2731,7 @@
       <c r="D2" s="21"/>
     </row>
     <row r="3" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="54" t="s">
         <v>618</v>
       </c>
       <c r="C3" s="26" t="s">
@@ -2740,7 +2740,7 @@
       <c r="D3" s="28"/>
     </row>
     <row r="4" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="54" t="s">
         <v>619</v>
       </c>
       <c r="C4" s="26" t="s">
@@ -2749,7 +2749,7 @@
       <c r="D4" s="28"/>
     </row>
     <row r="5" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="62" t="s">
+      <c r="B5" s="54" t="s">
         <v>620</v>
       </c>
       <c r="C5" s="26" t="s">
@@ -2758,7 +2758,7 @@
       <c r="D5" s="28"/>
     </row>
     <row r="6" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="62" t="s">
+      <c r="B6" s="54" t="s">
         <v>621</v>
       </c>
       <c r="C6" s="26" t="s">
@@ -2767,7 +2767,7 @@
       <c r="D6" s="28"/>
     </row>
     <row r="7" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="62" t="s">
+      <c r="B7" s="54" t="s">
         <v>622</v>
       </c>
       <c r="C7" s="26" t="s">
@@ -2776,7 +2776,7 @@
       <c r="D7" s="28"/>
     </row>
     <row r="8" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="62" t="s">
+      <c r="B8" s="54" t="s">
         <v>623</v>
       </c>
       <c r="C8" s="26" t="s">
@@ -2785,7 +2785,7 @@
       <c r="D8" s="28"/>
     </row>
     <row r="9" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="62" t="s">
+      <c r="B9" s="54" t="s">
         <v>624</v>
       </c>
       <c r="C9" s="26" t="s">
@@ -2794,7 +2794,7 @@
       <c r="D9" s="28"/>
     </row>
     <row r="10" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="62" t="s">
+      <c r="B10" s="54" t="s">
         <v>625</v>
       </c>
       <c r="C10" s="26" t="s">
@@ -2803,7 +2803,7 @@
       <c r="D10" s="28"/>
     </row>
     <row r="11" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="62" t="s">
+      <c r="B11" s="54" t="s">
         <v>626</v>
       </c>
       <c r="C11" s="26" t="s">
@@ -2812,7 +2812,7 @@
       <c r="D11" s="28"/>
     </row>
     <row r="12" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="62" t="s">
+      <c r="B12" s="54" t="s">
         <v>627</v>
       </c>
       <c r="C12" s="26" t="s">
@@ -2821,7 +2821,7 @@
       <c r="D12" s="28"/>
     </row>
     <row r="13" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="62" t="s">
+      <c r="B13" s="54" t="s">
         <v>628</v>
       </c>
       <c r="C13" s="26" t="s">
@@ -2830,7 +2830,7 @@
       <c r="D13" s="28"/>
     </row>
     <row r="14" spans="2:4" s="26" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="63" t="s">
+      <c r="B14" s="55" t="s">
         <v>629</v>
       </c>
       <c r="C14" s="44" t="s">
@@ -2885,34 +2885,34 @@
       </c>
     </row>
     <row r="2" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="59" t="s">
         <v>685</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="62" t="s">
         <v>641</v>
       </c>
       <c r="D2" s="47"/>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="61" t="s">
         <v>642</v>
       </c>
-      <c r="F2" s="57"/>
+      <c r="F2" s="61"/>
       <c r="G2" s="48"/>
-      <c r="H2" s="57" t="s">
+      <c r="H2" s="61" t="s">
         <v>645</v>
       </c>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
       <c r="L2" s="48"/>
-      <c r="M2" s="57" t="s">
+      <c r="M2" s="61" t="s">
         <v>646</v>
       </c>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
     </row>
     <row r="3" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="61"/>
-      <c r="C3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="63"/>
       <c r="D3" s="51"/>
       <c r="E3" s="50" t="s">
         <v>643</v>
@@ -4464,34 +4464,34 @@
       </c>
     </row>
     <row r="43" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="60" t="s">
+      <c r="B43" s="59" t="s">
         <v>685</v>
       </c>
-      <c r="C43" s="58" t="s">
+      <c r="C43" s="62" t="s">
         <v>641</v>
       </c>
       <c r="D43" s="47"/>
-      <c r="E43" s="57" t="s">
+      <c r="E43" s="61" t="s">
         <v>642</v>
       </c>
-      <c r="F43" s="57"/>
+      <c r="F43" s="61"/>
       <c r="G43" s="48"/>
-      <c r="H43" s="57" t="s">
+      <c r="H43" s="61" t="s">
         <v>645</v>
       </c>
-      <c r="I43" s="57"/>
-      <c r="J43" s="57"/>
-      <c r="K43" s="57"/>
+      <c r="I43" s="61"/>
+      <c r="J43" s="61"/>
+      <c r="K43" s="61"/>
       <c r="L43" s="48"/>
-      <c r="M43" s="57" t="s">
+      <c r="M43" s="61" t="s">
         <v>646</v>
       </c>
-      <c r="N43" s="57"/>
-      <c r="O43" s="57"/>
+      <c r="N43" s="61"/>
+      <c r="O43" s="61"/>
     </row>
     <row r="44" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="61"/>
-      <c r="C44" s="59"/>
+      <c r="B44" s="60"/>
+      <c r="C44" s="63"/>
       <c r="D44" s="51"/>
       <c r="E44" s="50" t="s">
         <v>643</v>
@@ -5265,34 +5265,34 @@
       </c>
     </row>
     <row r="65" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="60" t="s">
+      <c r="B65" s="59" t="s">
         <v>685</v>
       </c>
-      <c r="C65" s="58" t="s">
+      <c r="C65" s="62" t="s">
         <v>641</v>
       </c>
       <c r="D65" s="47"/>
-      <c r="E65" s="57" t="s">
+      <c r="E65" s="61" t="s">
         <v>642</v>
       </c>
-      <c r="F65" s="57"/>
+      <c r="F65" s="61"/>
       <c r="G65" s="48"/>
-      <c r="H65" s="57" t="s">
+      <c r="H65" s="61" t="s">
         <v>645</v>
       </c>
-      <c r="I65" s="57"/>
-      <c r="J65" s="57"/>
-      <c r="K65" s="57"/>
+      <c r="I65" s="61"/>
+      <c r="J65" s="61"/>
+      <c r="K65" s="61"/>
       <c r="L65" s="48"/>
-      <c r="M65" s="57" t="s">
+      <c r="M65" s="61" t="s">
         <v>646</v>
       </c>
-      <c r="N65" s="57"/>
-      <c r="O65" s="57"/>
+      <c r="N65" s="61"/>
+      <c r="O65" s="61"/>
     </row>
     <row r="66" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="61"/>
-      <c r="C66" s="59"/>
+      <c r="B66" s="60"/>
+      <c r="C66" s="63"/>
       <c r="D66" s="51"/>
       <c r="E66" s="50" t="s">
         <v>643</v>
@@ -6256,11 +6256,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="H65:K65"/>
     <mergeCell ref="M65:O65"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="C43:C44"/>
@@ -6271,6 +6266,11 @@
     <mergeCell ref="E43:F43"/>
     <mergeCell ref="H43:K43"/>
     <mergeCell ref="M43:O43"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="H65:K65"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6304,34 +6304,34 @@
       </c>
     </row>
     <row r="2" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="59" t="s">
         <v>685</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="62" t="s">
         <v>641</v>
       </c>
       <c r="D2" s="47"/>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="61" t="s">
         <v>642</v>
       </c>
-      <c r="F2" s="57"/>
+      <c r="F2" s="61"/>
       <c r="G2" s="48"/>
-      <c r="H2" s="57" t="s">
+      <c r="H2" s="61" t="s">
         <v>645</v>
       </c>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
       <c r="L2" s="48"/>
-      <c r="M2" s="57" t="s">
+      <c r="M2" s="61" t="s">
         <v>646</v>
       </c>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
     </row>
     <row r="3" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="61"/>
-      <c r="C3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="63"/>
       <c r="D3" s="51"/>
       <c r="E3" s="50" t="s">
         <v>643</v>
@@ -7883,34 +7883,34 @@
       </c>
     </row>
     <row r="43" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="60" t="s">
+      <c r="B43" s="59" t="s">
         <v>685</v>
       </c>
-      <c r="C43" s="58" t="s">
+      <c r="C43" s="62" t="s">
         <v>641</v>
       </c>
       <c r="D43" s="47"/>
-      <c r="E43" s="57" t="s">
+      <c r="E43" s="61" t="s">
         <v>642</v>
       </c>
-      <c r="F43" s="57"/>
+      <c r="F43" s="61"/>
       <c r="G43" s="48"/>
-      <c r="H43" s="57" t="s">
+      <c r="H43" s="61" t="s">
         <v>645</v>
       </c>
-      <c r="I43" s="57"/>
-      <c r="J43" s="57"/>
-      <c r="K43" s="57"/>
+      <c r="I43" s="61"/>
+      <c r="J43" s="61"/>
+      <c r="K43" s="61"/>
       <c r="L43" s="48"/>
-      <c r="M43" s="57" t="s">
+      <c r="M43" s="61" t="s">
         <v>646</v>
       </c>
-      <c r="N43" s="57"/>
-      <c r="O43" s="57"/>
+      <c r="N43" s="61"/>
+      <c r="O43" s="61"/>
     </row>
     <row r="44" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="61"/>
-      <c r="C44" s="59"/>
+      <c r="B44" s="60"/>
+      <c r="C44" s="63"/>
       <c r="D44" s="51"/>
       <c r="E44" s="50" t="s">
         <v>643</v>
@@ -8684,34 +8684,34 @@
       </c>
     </row>
     <row r="65" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="60" t="s">
+      <c r="B65" s="59" t="s">
         <v>685</v>
       </c>
-      <c r="C65" s="58" t="s">
+      <c r="C65" s="62" t="s">
         <v>641</v>
       </c>
       <c r="D65" s="47"/>
-      <c r="E65" s="57" t="s">
+      <c r="E65" s="61" t="s">
         <v>642</v>
       </c>
-      <c r="F65" s="57"/>
+      <c r="F65" s="61"/>
       <c r="G65" s="48"/>
-      <c r="H65" s="57" t="s">
+      <c r="H65" s="61" t="s">
         <v>645</v>
       </c>
-      <c r="I65" s="57"/>
-      <c r="J65" s="57"/>
-      <c r="K65" s="57"/>
+      <c r="I65" s="61"/>
+      <c r="J65" s="61"/>
+      <c r="K65" s="61"/>
       <c r="L65" s="48"/>
-      <c r="M65" s="57" t="s">
+      <c r="M65" s="61" t="s">
         <v>646</v>
       </c>
-      <c r="N65" s="57"/>
-      <c r="O65" s="57"/>
+      <c r="N65" s="61"/>
+      <c r="O65" s="61"/>
     </row>
     <row r="66" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="61"/>
-      <c r="C66" s="59"/>
+      <c r="B66" s="60"/>
+      <c r="C66" s="63"/>
       <c r="D66" s="51"/>
       <c r="E66" s="50" t="s">
         <v>643</v>
@@ -9675,11 +9675,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="H65:K65"/>
     <mergeCell ref="M65:O65"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="C43:C44"/>
@@ -9690,6 +9685,11 @@
     <mergeCell ref="E43:F43"/>
     <mergeCell ref="H43:K43"/>
     <mergeCell ref="M43:O43"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="H65:K65"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9723,34 +9723,34 @@
       </c>
     </row>
     <row r="2" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="59" t="s">
         <v>685</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="62" t="s">
         <v>641</v>
       </c>
       <c r="D2" s="47"/>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="61" t="s">
         <v>642</v>
       </c>
-      <c r="F2" s="57"/>
+      <c r="F2" s="61"/>
       <c r="G2" s="48"/>
-      <c r="H2" s="57" t="s">
+      <c r="H2" s="61" t="s">
         <v>645</v>
       </c>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
       <c r="L2" s="48"/>
-      <c r="M2" s="57" t="s">
+      <c r="M2" s="61" t="s">
         <v>646</v>
       </c>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
     </row>
     <row r="3" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="61"/>
-      <c r="C3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="63"/>
       <c r="D3" s="51"/>
       <c r="E3" s="50" t="s">
         <v>643</v>
@@ -11302,34 +11302,34 @@
       </c>
     </row>
     <row r="43" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="60" t="s">
+      <c r="B43" s="59" t="s">
         <v>685</v>
       </c>
-      <c r="C43" s="58" t="s">
+      <c r="C43" s="62" t="s">
         <v>641</v>
       </c>
       <c r="D43" s="47"/>
-      <c r="E43" s="57" t="s">
+      <c r="E43" s="61" t="s">
         <v>642</v>
       </c>
-      <c r="F43" s="57"/>
+      <c r="F43" s="61"/>
       <c r="G43" s="48"/>
-      <c r="H43" s="57" t="s">
+      <c r="H43" s="61" t="s">
         <v>645</v>
       </c>
-      <c r="I43" s="57"/>
-      <c r="J43" s="57"/>
-      <c r="K43" s="57"/>
+      <c r="I43" s="61"/>
+      <c r="J43" s="61"/>
+      <c r="K43" s="61"/>
       <c r="L43" s="48"/>
-      <c r="M43" s="57" t="s">
+      <c r="M43" s="61" t="s">
         <v>646</v>
       </c>
-      <c r="N43" s="57"/>
-      <c r="O43" s="57"/>
+      <c r="N43" s="61"/>
+      <c r="O43" s="61"/>
     </row>
     <row r="44" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="61"/>
-      <c r="C44" s="59"/>
+      <c r="B44" s="60"/>
+      <c r="C44" s="63"/>
       <c r="D44" s="51"/>
       <c r="E44" s="50" t="s">
         <v>643</v>
@@ -12103,34 +12103,34 @@
       </c>
     </row>
     <row r="65" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="60" t="s">
+      <c r="B65" s="59" t="s">
         <v>685</v>
       </c>
-      <c r="C65" s="58" t="s">
+      <c r="C65" s="62" t="s">
         <v>641</v>
       </c>
       <c r="D65" s="47"/>
-      <c r="E65" s="57" t="s">
+      <c r="E65" s="61" t="s">
         <v>642</v>
       </c>
-      <c r="F65" s="57"/>
+      <c r="F65" s="61"/>
       <c r="G65" s="48"/>
-      <c r="H65" s="57" t="s">
+      <c r="H65" s="61" t="s">
         <v>645</v>
       </c>
-      <c r="I65" s="57"/>
-      <c r="J65" s="57"/>
-      <c r="K65" s="57"/>
+      <c r="I65" s="61"/>
+      <c r="J65" s="61"/>
+      <c r="K65" s="61"/>
       <c r="L65" s="48"/>
-      <c r="M65" s="57" t="s">
+      <c r="M65" s="61" t="s">
         <v>646</v>
       </c>
-      <c r="N65" s="57"/>
-      <c r="O65" s="57"/>
+      <c r="N65" s="61"/>
+      <c r="O65" s="61"/>
     </row>
     <row r="66" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="61"/>
-      <c r="C66" s="59"/>
+      <c r="B66" s="60"/>
+      <c r="C66" s="63"/>
       <c r="D66" s="51"/>
       <c r="E66" s="50" t="s">
         <v>643</v>
@@ -13094,11 +13094,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="H65:K65"/>
     <mergeCell ref="M65:O65"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="C43:C44"/>
@@ -13109,6 +13104,11 @@
     <mergeCell ref="E43:F43"/>
     <mergeCell ref="H43:K43"/>
     <mergeCell ref="M43:O43"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="H65:K65"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13139,34 +13139,34 @@
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="59" t="s">
         <v>685</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="62" t="s">
         <v>641</v>
       </c>
       <c r="D2" s="47"/>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="61" t="s">
         <v>642</v>
       </c>
-      <c r="F2" s="57"/>
+      <c r="F2" s="61"/>
       <c r="G2" s="48"/>
-      <c r="H2" s="57" t="s">
+      <c r="H2" s="61" t="s">
         <v>645</v>
       </c>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
       <c r="L2" s="48"/>
-      <c r="M2" s="57" t="s">
+      <c r="M2" s="61" t="s">
         <v>646</v>
       </c>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
     </row>
     <row r="3" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="61"/>
-      <c r="C3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="63"/>
       <c r="D3" s="51"/>
       <c r="E3" s="50" t="s">
         <v>643</v>
@@ -14718,34 +14718,34 @@
       </c>
     </row>
     <row r="43" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="60" t="s">
+      <c r="B43" s="59" t="s">
         <v>685</v>
       </c>
-      <c r="C43" s="58" t="s">
+      <c r="C43" s="62" t="s">
         <v>641</v>
       </c>
       <c r="D43" s="47"/>
-      <c r="E43" s="57" t="s">
+      <c r="E43" s="61" t="s">
         <v>642</v>
       </c>
-      <c r="F43" s="57"/>
+      <c r="F43" s="61"/>
       <c r="G43" s="48"/>
-      <c r="H43" s="57" t="s">
+      <c r="H43" s="61" t="s">
         <v>645</v>
       </c>
-      <c r="I43" s="57"/>
-      <c r="J43" s="57"/>
-      <c r="K43" s="57"/>
+      <c r="I43" s="61"/>
+      <c r="J43" s="61"/>
+      <c r="K43" s="61"/>
       <c r="L43" s="48"/>
-      <c r="M43" s="57" t="s">
+      <c r="M43" s="61" t="s">
         <v>646</v>
       </c>
-      <c r="N43" s="57"/>
-      <c r="O43" s="57"/>
+      <c r="N43" s="61"/>
+      <c r="O43" s="61"/>
     </row>
     <row r="44" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="61"/>
-      <c r="C44" s="59"/>
+      <c r="B44" s="60"/>
+      <c r="C44" s="63"/>
       <c r="D44" s="51"/>
       <c r="E44" s="50" t="s">
         <v>643</v>
@@ -15519,34 +15519,34 @@
       </c>
     </row>
     <row r="65" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="60" t="s">
+      <c r="B65" s="59" t="s">
         <v>685</v>
       </c>
-      <c r="C65" s="58" t="s">
+      <c r="C65" s="62" t="s">
         <v>641</v>
       </c>
       <c r="D65" s="47"/>
-      <c r="E65" s="57" t="s">
+      <c r="E65" s="61" t="s">
         <v>642</v>
       </c>
-      <c r="F65" s="57"/>
+      <c r="F65" s="61"/>
       <c r="G65" s="48"/>
-      <c r="H65" s="57" t="s">
+      <c r="H65" s="61" t="s">
         <v>645</v>
       </c>
-      <c r="I65" s="57"/>
-      <c r="J65" s="57"/>
-      <c r="K65" s="57"/>
+      <c r="I65" s="61"/>
+      <c r="J65" s="61"/>
+      <c r="K65" s="61"/>
       <c r="L65" s="48"/>
-      <c r="M65" s="57" t="s">
+      <c r="M65" s="61" t="s">
         <v>646</v>
       </c>
-      <c r="N65" s="57"/>
-      <c r="O65" s="57"/>
+      <c r="N65" s="61"/>
+      <c r="O65" s="61"/>
     </row>
     <row r="66" spans="2:18" s="49" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="61"/>
-      <c r="C66" s="59"/>
+      <c r="B66" s="60"/>
+      <c r="C66" s="63"/>
       <c r="D66" s="51"/>
       <c r="E66" s="50" t="s">
         <v>643</v>
@@ -16510,11 +16510,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="H65:K65"/>
     <mergeCell ref="M65:O65"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="C43:C44"/>
@@ -16525,6 +16520,11 @@
     <mergeCell ref="E43:F43"/>
     <mergeCell ref="H43:K43"/>
     <mergeCell ref="M43:O43"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="H65:K65"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16652,10 +16652,10 @@
       <c r="F12" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="54" t="s">
+      <c r="G12" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="54"/>
+      <c r="H12" s="56"/>
     </row>
     <row r="13" spans="1:20" s="22" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="21"/>
@@ -27188,10 +27188,10 @@
       <c r="F14" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="55" t="s">
+      <c r="G14" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="55"/>
+      <c r="H14" s="57"/>
     </row>
     <row r="15" spans="1:20" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26"/>
@@ -35884,25 +35884,25 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="8"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>159</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="56"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="58"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="58"/>
+      <c r="P2" s="58"/>
+      <c r="Q2" s="58"/>
+      <c r="R2" s="58"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B3" s="6" t="s">
@@ -36127,25 +36127,25 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="8"/>
-      <c r="B9" s="56" t="s">
+      <c r="B9" s="58" t="s">
         <v>178</v>
       </c>
-      <c r="C9" s="56"/>
-      <c r="D9" s="56"/>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="56"/>
-      <c r="K9" s="56"/>
-      <c r="L9" s="56"/>
-      <c r="M9" s="56"/>
-      <c r="N9" s="56"/>
-      <c r="O9" s="56"/>
-      <c r="P9" s="56"/>
-      <c r="Q9" s="56"/>
-      <c r="R9" s="56"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="58"/>
+      <c r="K9" s="58"/>
+      <c r="L9" s="58"/>
+      <c r="M9" s="58"/>
+      <c r="N9" s="58"/>
+      <c r="O9" s="58"/>
+      <c r="P9" s="58"/>
+      <c r="Q9" s="58"/>
+      <c r="R9" s="58"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B10" s="6" t="s">
@@ -36370,25 +36370,25 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
-      <c r="B16" s="56" t="s">
+      <c r="B16" s="58" t="s">
         <v>179</v>
       </c>
-      <c r="C16" s="56"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="56"/>
-      <c r="J16" s="56"/>
-      <c r="K16" s="56"/>
-      <c r="L16" s="56"/>
-      <c r="M16" s="56"/>
-      <c r="N16" s="56"/>
-      <c r="O16" s="56"/>
-      <c r="P16" s="56"/>
-      <c r="Q16" s="56"/>
-      <c r="R16" s="56"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="58"/>
+      <c r="K16" s="58"/>
+      <c r="L16" s="58"/>
+      <c r="M16" s="58"/>
+      <c r="N16" s="58"/>
+      <c r="O16" s="58"/>
+      <c r="P16" s="58"/>
+      <c r="Q16" s="58"/>
+      <c r="R16" s="58"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
@@ -36801,10 +36801,10 @@
       <c r="F12" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="54" t="s">
+      <c r="G12" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="54"/>
+      <c r="H12" s="56"/>
     </row>
     <row r="13" spans="1:20" s="22" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="21"/>
@@ -47357,10 +47357,10 @@
       <c r="F14" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="55" t="s">
+      <c r="G14" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="55"/>
+      <c r="H14" s="57"/>
     </row>
     <row r="15" spans="1:20" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26"/>
@@ -56053,25 +56053,25 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="8"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>159</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="56"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="58"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="58"/>
+      <c r="P2" s="58"/>
+      <c r="Q2" s="58"/>
+      <c r="R2" s="58"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B3" s="6" t="s">
@@ -56296,25 +56296,25 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="8"/>
-      <c r="B9" s="56" t="s">
+      <c r="B9" s="58" t="s">
         <v>178</v>
       </c>
-      <c r="C9" s="56"/>
-      <c r="D9" s="56"/>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="56"/>
-      <c r="K9" s="56"/>
-      <c r="L9" s="56"/>
-      <c r="M9" s="56"/>
-      <c r="N9" s="56"/>
-      <c r="O9" s="56"/>
-      <c r="P9" s="56"/>
-      <c r="Q9" s="56"/>
-      <c r="R9" s="56"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="58"/>
+      <c r="K9" s="58"/>
+      <c r="L9" s="58"/>
+      <c r="M9" s="58"/>
+      <c r="N9" s="58"/>
+      <c r="O9" s="58"/>
+      <c r="P9" s="58"/>
+      <c r="Q9" s="58"/>
+      <c r="R9" s="58"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B10" s="6" t="s">
@@ -56539,25 +56539,25 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
-      <c r="B16" s="56" t="s">
+      <c r="B16" s="58" t="s">
         <v>179</v>
       </c>
-      <c r="C16" s="56"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="56"/>
-      <c r="J16" s="56"/>
-      <c r="K16" s="56"/>
-      <c r="L16" s="56"/>
-      <c r="M16" s="56"/>
-      <c r="N16" s="56"/>
-      <c r="O16" s="56"/>
-      <c r="P16" s="56"/>
-      <c r="Q16" s="56"/>
-      <c r="R16" s="56"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="58"/>
+      <c r="K16" s="58"/>
+      <c r="L16" s="58"/>
+      <c r="M16" s="58"/>
+      <c r="N16" s="58"/>
+      <c r="O16" s="58"/>
+      <c r="P16" s="58"/>
+      <c r="Q16" s="58"/>
+      <c r="R16" s="58"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
